--- a/weekly_message/0607_일.xlsx
+++ b/weekly_message/0607_일.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\[중1] - 1학기 진도 사항\TextMessage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9191h\Desktop\[중1] - 1학기 진도 사항\weekly_message\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87044D7C-8414-4F31-92A3-B4E753C67B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFBA17F-F0B8-4AED-AE77-1627A903AE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
   <si>
     <t>주테
 점수</t>
@@ -129,6 +129,11 @@
   </si>
   <si>
     <t>문법</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -136,7 +141,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -195,8 +200,15 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +263,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -279,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,6 +346,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,7 +579,7 @@
     <col min="9" max="9" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.06640625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="53.46484375" style="10" customWidth="1"/>
     <col min="15" max="15" width="8.265625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.265625" bestFit="1" customWidth="1"/>
@@ -610,7 +631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -627,7 +648,9 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="M2" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N2" s="9" t="str">
         <f t="shared" ref="N2:N11" si="1">"▷ "&amp;B2&amp;"는 이번 주간 테스트에서 "&amp;C2&amp;"점을 받았습니다."&amp;CHAR(10)&amp;
 IF(C2=100,"",
@@ -649,10 +672,12 @@
         <v>▷ 시우는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
@@ -669,16 +694,20 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="M3" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N3" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 윤건이는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -695,16 +724,20 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="M4" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N4" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 예승이는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
@@ -721,16 +754,20 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="M5" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N5" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 다은이는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
         <v>12</v>
       </c>
@@ -747,16 +784,20 @@
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="M6" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N6" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 민지는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B7" s="16" t="s">
         <v>13</v>
       </c>
@@ -773,16 +814,20 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="M7" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N7" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 서율이는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
@@ -799,16 +844,20 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="M8" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N8" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 다현이는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B9" s="16" t="s">
         <v>19</v>
       </c>
@@ -825,16 +874,20 @@
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="M9" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N9" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 정무는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
         <v>15</v>
       </c>
@@ -851,16 +904,20 @@
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="M10" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N10" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 도후는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B11" s="16" t="s">
         <v>16</v>
       </c>
@@ -877,16 +934,20 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="M11" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N11" s="9" t="str">
         <f t="shared" si="1"/>
         <v>▷ 예나는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B12" s="16" t="s">
         <v>17</v>
       </c>
@@ -903,7 +964,9 @@
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="M12" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N12" s="9" t="str">
         <f t="shared" ref="N12:N14" si="3">"▷ "&amp;B12&amp;"는 이번 주간 테스트에서 "&amp;C12&amp;"점을 받았습니다."&amp;CHAR(10)&amp;
 IF(C12=100,"",
@@ -925,10 +988,12 @@
         <v>▷ 은서는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="216.75" x14ac:dyDescent="0.35">
       <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
@@ -945,13 +1010,17 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="M13" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="N13" s="9" t="str">
         <f t="shared" si="3"/>
         <v>▷ 윤슬이는 이번 주간 테스트에서 100점을 받았습니다.
 ▷ 과 제 : 우수
 ▷ 수 업 : 우수
-※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.</v>
+※ 과제와 수업에 특이사항이 있으면 전달 드리겠습니다.
+※ 1월부터 시작된 학기가 어느덧 마지막을 향해 가고 있습니다. 아이들이 과제 수행에는 많이 익숙해졌지만, 최근에는 문제를 꼼꼼하게 확인하기보다 피상적으로 해결하려는 모습이 자주 보이고 있습니다.
+날씨가 점점 더워지면서 체력적으로 쉽게 지칠 수 있는 시기이지만, 과제를 수행할 때만큼은 조금 더 집중해서 끝까지 꼼꼼하게 확인하는 습관을 유지할 수 있도록 가정에서도 많은 격려 부탁드립니다.</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="89.25" x14ac:dyDescent="0.35">
